--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2022_metropolitana.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2022_metropolitana.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:01</t>
+    <t xml:space="preserve">2026-09-09 19:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2022_metropolitana.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2022_metropolitana.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:34</t>
+    <t xml:space="preserve">2026-09-16 16:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2022_metropolitana.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2022_metropolitana.xlsx
@@ -6,29 +6,32 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sexo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Edades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Comunas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Edades'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comunas'!$A$1:$D$53</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t xml:space="preserve">Categoría</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saldo migratorio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hombres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mujeres</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+  <si>
+    <t xml:space="preserve">Cambiaron de comuna dentro de la región</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cruzaron el límite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llegaron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se fueron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saldo de la región</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -40,7 +43,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-16 16:33</t>
+    <t xml:space="preserve">2026-09-30 09:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -58,31 +61,187 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">M_SALDOMIGR_a</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Región de Metropolitana</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
   </si>
   <si>
-    <t xml:space="preserve">Tramo de edad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 a 4 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 a 14 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 a 29 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 a 59 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60 años o más</t>
+    <t xml:space="preserve">2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con otras regiones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con otras comunas de la región</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saldo de la comuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Condes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Providencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuñoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lampa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calera de Tango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Padre Hurtado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Barnechea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitacura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pirque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curacaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isla de Maipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Miguel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talagante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San José de Maipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerrillos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Reina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñaflor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Monte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">María Pinto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Espejo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cisterna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alhué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pedro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiltil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Joaquín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huechuraba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Ramón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Granja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Florida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedro Aguirre Cerda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Bernardo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilicura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinta Normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerro Navia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conchalí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Pintana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Prado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñalolén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pudahuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Bosque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estación Central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recoleta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puente Alto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maipú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santiago</t>
   </si>
 </sst>
 </file>
@@ -447,8 +606,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="11.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="18.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="40.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,25 +620,35 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
+      <c r="A2" s="2" t="n">
+        <v>600904</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-86118</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>-66400</v>
+        <v>388272</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>117877</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>270395</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>-152518</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:E2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -493,58 +665,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -558,60 +730,756 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="18.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="21.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="32.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>-4880</v>
+        <v>-509</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>7696</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>7187</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>-13164</v>
+        <v>-193</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>7127</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>6934</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>-25347</v>
+        <v>-1143</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>6541</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>5398</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>-93129</v>
+        <v>-1283</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>4795</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>3512</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-15998</v>
+        <v>-195</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>3384</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>3189</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>-761</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>3882</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>3121</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>-889</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>4009</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>-551</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>3627</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>3076</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>-421</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>3062</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>2641</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>-107</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>2367</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>-1544</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>3730</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>-735</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>2109</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>-141</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1327</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>-66</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1213</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>-1309</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>2154</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>-445</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>-117</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>789</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>-828</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>1466</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>-702</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>1308</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>-870</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>1297</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>-213</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>633</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>-65</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>414</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>-1028</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>1344</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>-934</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>1240</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>-46</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>277</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>-1288</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>1284</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>-204</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>-138</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>-1252</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>875</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>-377</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>-986</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>561</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>-425</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>-1123</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>680</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>-443</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>-998</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>543</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>-455</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>-915</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>-30</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>-945</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>-1484</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>410</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>-1074</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>-4436</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>3275</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>-1161</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>-862</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>-371</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>-1233</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>-3557</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>-1557</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>-2462</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>742</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>-1720</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>-1272</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>-803</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>-2075</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>-2005</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>-176</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>-2181</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>-1694</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>-511</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>-2205</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>-1287</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>-975</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>-2262</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>-2599</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>269</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>-2330</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>-1358</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>-1218</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>-2576</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>-3120</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>282</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>-2838</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>-2754</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>-404</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>-3158</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>-2070</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>-1170</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>-3240</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>-1635</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>-1811</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>-3446</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>-1701</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>-2611</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>-4312</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>-8706</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>-651</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>-9357</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>-7589</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>-2270</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>-9859</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>-80064</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>-65168</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>-145232</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:D53"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2022_metropolitana.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2022_metropolitana.xlsx
@@ -43,7 +43,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30 09:58</t>
+    <t xml:space="preserve">2026-10-05 03:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
